--- a/data-vh/Июнь_2026_ВХ.xlsx
+++ b/data-vh/Июнь_2026_ВХ.xlsx
@@ -2,39 +2,55 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="22320" windowHeight="13176" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Лист_1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Лист_1'!$A$1:$Q$28</definedName>
+  </definedNames>
+  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="R1C1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
+  <fonts count="3">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
+      <name val="Arial"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="8"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4ECC5"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -42,15 +58,149 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCC085"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCC085"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCC085"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCC085"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCC085"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFCCC085"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCC085"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFCCC085"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCC085"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -125,9 +275,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -165,7 +315,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -199,6 +349,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -233,9 +384,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -410,1874 +562,2011 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="10.42578125" defaultRowHeight="11.4" customHeight="1"/>
+  <cols>
+    <col width="5.140625" customWidth="1" style="1" min="1" max="1"/>
+    <col width="5.28515625" customWidth="1" style="1" min="2" max="2"/>
+    <col width="3.7109375" customWidth="1" style="1" min="3" max="3"/>
+    <col width="5" customWidth="1" style="1" min="4" max="4"/>
+    <col width="10.140625" customWidth="1" style="1" min="5" max="5"/>
+    <col width="22.5703125" customWidth="1" style="1" min="6" max="6"/>
+    <col width="21" customWidth="1" style="1" min="7" max="7"/>
+    <col width="29.7109375" customWidth="1" style="1" min="8" max="8"/>
+    <col width="18.5703125" customWidth="1" style="1" min="9" max="9"/>
+    <col width="32.140625" customWidth="1" style="1" min="10" max="10"/>
+    <col width="13.7109375" customWidth="1" style="1" min="11" max="11"/>
+    <col width="7.28515625" customWidth="1" style="1" min="12" max="12"/>
+    <col width="8.28515625" customWidth="1" style="1" min="13" max="13"/>
+    <col width="27.5703125" customWidth="1" style="1" min="14" max="14"/>
+    <col width="30.7109375" customWidth="1" style="1" min="15" max="15"/>
+    <col width="74.7109375" customWidth="1" style="1" min="16" max="16"/>
+    <col width="44.28515625" customWidth="1" style="1" min="17" max="17"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="25.95" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>№ п/п</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Номер</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="C1" s="21" t="n"/>
+      <c r="D1" s="22" t="n"/>
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>Дата</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="17" t="inlineStr">
         <is>
           <t>Основание</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="18" t="inlineStr">
         <is>
           <t>Поставщик/Переработчик</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="15" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="15" t="inlineStr">
         <is>
           <t>Место проведения контроля</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="15" t="inlineStr">
         <is>
           <t>Номенклатура</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="15" t="inlineStr">
         <is>
           <t>Группа номенклатуры</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="15" t="inlineStr">
         <is>
           <t>Кол., шт.</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="15" t="inlineStr">
         <is>
           <t>Кол., кг</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="15" t="inlineStr">
         <is>
           <t>Вид несоответствия</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="15" t="inlineStr">
         <is>
           <t>Критичность несоответствия</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="15" t="inlineStr">
         <is>
           <t>Несоответствие</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="15" t="inlineStr">
         <is>
           <t>Решение</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="2" ht="34.95" customHeight="1">
+      <c r="A2" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>В00-0000084</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="C2" s="21" t="n"/>
+      <c r="D2" s="22" t="n"/>
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>01.06.2026</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="F2" s="5" t="n"/>
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>Монтажторгстрой ООО</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>_Склад корпус №11</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>(ПФ(закупка)) Пластина (32х570х2380) (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>МК, другое</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2" s="10" t="n">
         <v>1546.95</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2" s="7" t="inlineStr">
         <is>
           <t>Размер 2380+-2мм, фактически 2384мм (1шт). Отсутствует кромка 20+-0,3*3+-1.Размер 55+-0,4мм, фактически 53,69-56,81мм. Заусенцы. Остатки силиконового герметика..</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены силами работников УМИ</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" ht="34.95" customHeight="1">
+      <c r="A3" s="3" t="n">
         <v>151</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>В00-0000085</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="C3" s="21" t="n"/>
+      <c r="D3" s="22" t="n"/>
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>02.06.2026</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000285 от 02.06.2026 9:21:20</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>АСТРЕЯ ООО (ЭДО Такском ЗП согл. от 19.03.2025)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>ПФК(закупка) Элемент закладной ЗФ-30/4/К300-4,5  (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3" s="14" t="n">
         <v>3058.3</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" s="7" t="inlineStr">
         <is>
           <t>По ГОСТ 14771: ширина сварного шва С17 12+-2мм, фактически 6,4-15,4мм, высота сварного шва С17 1+-1мм, фактически до -0,77мм. Подрез (1шт). Натеки металла сварного шва У4 (1шт).</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q3" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены силами переработчика</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" ht="22.95" customHeight="1">
+      <c r="A4" s="3" t="n">
         <v>152</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>В00-0000086</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="C4" s="21" t="n"/>
+      <c r="D4" s="22" t="n"/>
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>02.06.2026</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>Приобретение товаров и услуг 0000-001983 от 14.05.2026 0:00:00</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="20" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>МЕТАЛЛСЕРВИС-МОСКВА ООО</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>Корпус №13</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>_уу_Полоса 5,0*30*6000 ГОСТ 103-2006/ Ст3сп</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="7" t="inlineStr">
         <is>
           <t>Листы сталь Ст3сп, Ст3сп5 (С255, Ст2сп)</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="L4" s="3" t="n">
         <v>59</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4" s="11" t="n">
         <v>417.012</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N4" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O4" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  В лом;</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P4" s="7" t="inlineStr">
         <is>
           <t>По ГОСТ 103 длина 6000+50 мм, фактически 875-6000 мм. Имеются дефекты ввиде перегиба (загиба, залома).</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
+      <c r="Q4" s="7" t="n"/>
+    </row>
+    <row r="5" ht="70.95" customHeight="1">
+      <c r="A5" s="3" t="n">
         <v>153</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>В00-0000087</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="C5" s="21" t="n"/>
+      <c r="D5" s="22" t="n"/>
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>02.06.2026</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000269 от 30.05.2026 16:35:59</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Настил SP 34х38/25х2 S4 А 730х750 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" s="7" t="inlineStr">
         <is>
           <t>Настилы сварные</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="L5" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5" s="8" t="n">
         <v>243.6</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N5" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O5" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P5" s="7" t="inlineStr">
         <is>
           <t>Выступание связующих элементов по СТО не более 1,5мм, фактически до 5мм. Занижение обрамляющего элемента по СТО не более 1мм, фактически до 5мм. Выступание обрамляющего элемента по СТО не более 1мм, фактически до 3мм. Выгнутость по СТО не более 8мм, фактически до 11мм. Механические повреждения. Дефекты сварных швов: брызги металла, кратеры, поры, натёки, прожоги, несплавления.</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
+      <c r="Q5" s="7" t="n"/>
+    </row>
+    <row r="6" ht="58.95" customHeight="1">
+      <c r="A6" s="3" t="n">
         <v>154</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>В00-0000088</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="C6" s="21" t="n"/>
+      <c r="D6" s="22" t="n"/>
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>02.06.2026</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>ТЗМИК АЛЬТАИР ООО</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="I6" s="7" t="n"/>
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>ГПОкр(240) Кронштейн КП</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" s="7" t="inlineStr">
         <is>
           <t>МК, другое</t>
         </is>
       </c>
-      <c r="L6" t="n">
+      <c r="L6" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6" s="8" t="n">
         <v>731.2</v>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N6" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O6" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P6" s="7" t="inlineStr">
         <is>
           <t>1.На локальных участках дефекты сварных швов: брызги металла, плохое повторное возбуждение дуги. Доработано в процессе контроля сотрудником ОА «Завод Продмаш».    2.Разнооттеночность очищенной поверхности от светло-серого до темно-серого цвета, на торцевых поверхностях деталей и отверстий «бурая ржавчина».     Шероховатость поверхности Rz от 30 до 80 мкм.</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Q6" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="7" ht="46.95" customHeight="1">
+      <c r="A7" s="3" t="n">
         <v>155</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>В00-0000089</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="C7" s="21" t="n"/>
+      <c r="D7" s="22" t="n"/>
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>03.06.2026</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>ТЗМИК АЛЬТАИР ООО</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>ТЗМИК АЛЬТАИР ООО</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>ГПОкр(240) Кронштейн КП</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" s="7" t="inlineStr">
         <is>
           <t>МК, другое</t>
         </is>
       </c>
-      <c r="L7" t="n">
+      <c r="L7" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7" s="10" t="n">
         <v>1608.64</v>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N7" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O7" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P7" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов:    Поры, плохое повторное возбуждение дуги, отсутствие плавного перехода к основному металлу. Устранено в процессе контроля.     Состояние поверхности:    "бурая ржавчина" на локальных участках.     На двух изделиях шероховатость от 9 до 54 мкм (ср. 33 мкм), от 7 до 54 мкм (ср. 29 мкм)</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Q7" s="7" t="inlineStr">
         <is>
           <t>Проведен контроль после повторной дробеструйной обработки, несоответствия не выявлены</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="8" ht="46.95" customHeight="1">
+      <c r="A8" s="3" t="n">
         <v>156</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>В00-0000090</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="C8" s="21" t="n"/>
+      <c r="D8" s="22" t="n"/>
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>09.06.2026</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>ТЗМИК АЛЬТАИР ООО</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="I8" s="7" t="n"/>
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>ГПОкр(240) Кронштейн КП</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" s="7" t="inlineStr">
         <is>
           <t>МК, другое</t>
         </is>
       </c>
-      <c r="L8" t="n">
+      <c r="L8" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8" s="14" t="n">
         <v>1462.4</v>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N8" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="O8" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P8" s="7" t="inlineStr">
         <is>
           <t>После нанесения финишного слоя. Класс покрытия V, средняя толщина 350 – 399 мкм, 90/10 – выполнено.    Локальные участки с толщинами менее 265 мкм доработаны в процессе контроля.    На двух изделиях повреждения финишного слоя до грунта.</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Q8" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
+    <row r="9" ht="22.95" customHeight="1">
+      <c r="A9" s="3" t="n">
         <v>157</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>В00-0000090</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="C9" s="21" t="n"/>
+      <c r="D9" s="22" t="n"/>
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>09.06.2026</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>ТЗМИК АЛЬТАИР ООО</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="I9" s="7" t="n"/>
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>ГПОкр(240) Кронштейн КП</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K9" s="7" t="inlineStr">
         <is>
           <t>МК, другое</t>
         </is>
       </c>
-      <c r="L9" t="n">
+      <c r="L9" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9" s="9" t="n">
         <v>877.4400000000001</v>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N9" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O9" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P9" s="7" t="inlineStr">
         <is>
           <t>После нанесения второго слоя грунта. Класс покрытия V, средняя толщина 360 – 410 мкм, 90/10 – выполнено.</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
+      <c r="Q9" s="7" t="n"/>
+    </row>
+    <row r="10" ht="22.95" customHeight="1">
+      <c r="A10" s="3" t="n">
         <v>158</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>В00-0000091</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="C10" s="21" t="n"/>
+      <c r="D10" s="22" t="n"/>
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>10.06.2026</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000330 от 09.06.2026 15:09:30</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>АСТРЕЯ ООО (ЭДО Такском ЗП согл. от 19.03.2025)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="7" t="inlineStr">
         <is>
           <t>ПФК(закупка) Элемент закладной ЗФ-24/4/К230-2,5 (ЭЗ 249.00.00.000 СБ)  (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K10" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L10" t="n">
+      <c r="L10" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10" s="9" t="n">
         <v>457.65</v>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N10" s="7" t="inlineStr">
         <is>
           <t>Не выполнено притупление кромок/ скругление</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="O10" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P10" s="7" t="inlineStr">
         <is>
           <t>Не выполнено притупление кромок</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Q10" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены УМИ</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
+    <row r="11" ht="22.95" customHeight="1">
+      <c r="A11" s="3" t="n">
         <v>159</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>В00-0000092</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="C11" s="21" t="n"/>
+      <c r="D11" s="22" t="n"/>
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>10.06.2026</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000328 от 09.06.2026 10:13:01</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>АСТРЕЯ ООО (ЭДО Такском ЗП согл. от 19.03.2025)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>ПФК(закупка) Элемент закладной ЗФ-24/4/К230-2,5 (ЭЗ 249.00.00.000 СБ)  (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L11" t="n">
+      <c r="L11" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11" s="9" t="n">
         <v>457.65</v>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N11" s="7" t="inlineStr">
         <is>
           <t>Не выполнено притупление кромок/ скругление</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O11" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P11" s="7" t="inlineStr">
         <is>
           <t>Не выполнено притупление кромок</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Q11" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены УМИ</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
+    <row r="12" ht="22.95" customHeight="1">
+      <c r="A12" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>В00-0000093</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="C12" s="21" t="n"/>
+      <c r="D12" s="22" t="n"/>
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>10.06.2026</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="19" t="inlineStr">
         <is>
           <t>Приобретение товаров и услуг 0000-002480 от 08.06.2026 0:00:00</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>МЕТАЛЛОТОРГ АО (ЭДО Такском ПМ, ЗП+)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>Основной склад</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>_уу_Труба 15*2,8 ГОСТ 3262-75/ Ст3сп, Ст3сп5 (С255, Ст2сп)</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K12" s="7" t="inlineStr">
         <is>
           <t>2.1.1.2.1.8 Трубы стальные водогазопроводные ГОСТ 3262-75</t>
         </is>
       </c>
-      <c r="L12" t="n">
+      <c r="L12" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N12" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O12" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  В лом;</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P12" s="7" t="inlineStr">
         <is>
           <t>Содержание кремния 0,02-0,04% (ГОСТ 380 сталь Ст3сп содержание кремния 0,15-0,30%).</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
+      <c r="Q12" s="7" t="n"/>
+    </row>
+    <row r="13" ht="22.95" customHeight="1">
+      <c r="A13" s="3" t="n">
         <v>161</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>В00-0000094</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="C13" s="21" t="n"/>
+      <c r="D13" s="22" t="n"/>
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t>11.06.2026</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000342 от 11.06.2026 9:31:44</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>АСТРЕЯ ООО (ЭДО Такском ЗП согл. от 19.03.2025)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Настил Р 44,4х11,1/30х3 А 715х1380 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K13" s="7" t="inlineStr">
         <is>
           <t>Настилы прессованные</t>
         </is>
       </c>
-      <c r="L13" t="n">
+      <c r="L13" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13" s="14" t="n">
         <v>1576.2</v>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N13" s="7" t="inlineStr">
         <is>
           <t>Разность диагоналей настила</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O13" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P13" s="7" t="inlineStr">
         <is>
           <t>Разность диагоналей настила фактически 15-17 мм (по СТО 07525912-050-2024 табл. В.1 не более 0,01*1380=13,8 мм)</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Q13" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены силами переработчика</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
+    <row r="14" ht="34.95" customHeight="1">
+      <c r="A14" s="3" t="n">
         <v>162</v>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>В00-0000095</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="C14" s="21" t="n"/>
+      <c r="D14" s="22" t="n"/>
+      <c r="E14" s="16" t="inlineStr">
         <is>
           <t>16.06.2026</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000353 от 16.06.2026 8:39:56</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>АСТРЕЯ ООО (ЭДО Такском ЗП согл. от 19.03.2025)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>ПФК(закупка) Элемент закладной ЗФ-24/4/К230-2,5 (ЭЗ 249.00.00.000 СБ)  (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K14" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L14" t="n">
+      <c r="L14" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M14" s="9" t="n">
         <v>183.06</v>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N14" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="O14" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="P14" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов: 1. Брызги металла. 2. Поры. Дефекты термической резки: 1. Неполный рез. 2. Налипший шлак.  Несоответствия требованиям КД: 1. Не выполнено притуплние кромок дет.3.</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="Q14" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="n">
+    <row r="15" ht="22.95" customHeight="1">
+      <c r="A15" s="3" t="n">
         <v>163</v>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>В00-0000096</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="C15" s="21" t="n"/>
+      <c r="D15" s="22" t="n"/>
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>16.06.2026</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000357 от 16.06.2026 13:20:28</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>АСТРЕЯ ООО (ЭДО Такском ЗП согл. от 19.03.2025)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>ПФК(закупка) Кронштейн 1.К2-2,0-1,5-0/180-Ф4 (МС 866.00.00.000 СБ)  (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K15" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L15" t="n">
+      <c r="L15" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M15" s="8" t="n">
         <v>29.5</v>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N15" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="O15" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P15" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов: Подрез. Несоответствия требованиям КД: Отсутствуют  технологические отверстия на детали 3</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
+      <c r="Q15" s="7" t="n"/>
+    </row>
+    <row r="16" ht="22.95" customHeight="1">
+      <c r="A16" s="3" t="n">
         <v>164</v>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>В00-0000097</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="C16" s="21" t="n"/>
+      <c r="D16" s="22" t="n"/>
+      <c r="E16" s="16" t="inlineStr">
         <is>
           <t>18.06.2026</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000364 от 18.06.2026 13:50:28</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>АСТРЕЯ ООО (ЭДО Такском ЗП согл. от 19.03.2025)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>ПФК(закупка) Элемент закладной ЗФ-30/4/К300-4,5  (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K16" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L16" t="n">
+      <c r="L16" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M16" s="10" t="n">
         <v>1092.25</v>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="N16" s="7" t="inlineStr">
         <is>
           <t>Не выполнено притупление кромок/ скругление</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="O16" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="P16" s="7" t="inlineStr">
         <is>
           <t>Не выполнено притупление кромок детал поз.4</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="Q16" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены УМИ</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
+    <row r="17" ht="22.95" customHeight="1">
+      <c r="A17" s="3" t="n">
         <v>165</v>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>В00-0000098</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="C17" s="21" t="n"/>
+      <c r="D17" s="22" t="n"/>
+      <c r="E17" s="16" t="inlineStr">
         <is>
           <t>17.06.2026</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr">
         <is>
           <t>МК ВОЛГАДОН ООО (ЭДО Таксом ЗП согл 21.05.2024)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" s="7" t="inlineStr">
         <is>
           <t>МК ВОЛГАДОН ООО (ЭДО Таксом ЗП согл 21.05.2024)</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Стойка СП11 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K17" s="7" t="inlineStr">
         <is>
           <t>РО</t>
         </is>
       </c>
-      <c r="L17" t="n">
+      <c r="L17" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M17" s="10" t="n">
         <v>3601.75</v>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N17" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="O17" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="P17" s="7" t="inlineStr">
         <is>
           <t>Плохое повторное ывозобнавление дуги, брызги металла, пора.</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
+      <c r="Q17" s="7" t="n"/>
+    </row>
+    <row r="18" ht="22.95" customHeight="1">
+      <c r="A18" s="3" t="n">
         <v>166</v>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>В00-0000099</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="C18" s="21" t="n"/>
+      <c r="D18" s="22" t="n"/>
+      <c r="E18" s="16" t="inlineStr">
         <is>
           <t>18.06.2026</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="19" t="inlineStr">
         <is>
           <t>Приобретение товаров и услуг 0000-002670 от 18.06.2026 14:45:21</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="20" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H18" s="7" t="inlineStr">
         <is>
           <t>СамараПромснаб ПК</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" s="7" t="inlineStr">
         <is>
           <t>Основной склад</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>(ОО_ПФ) Втулка МФГ-М 001.20.20.002 (резка в размер), (опытный образец)</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K18" s="7" t="inlineStr">
         <is>
           <t>Проект ЗАВЕРШЕН "Модернизация конструктива короны и оголовка" 1-000000083 Ушков А.В.</t>
         </is>
       </c>
-      <c r="L18" t="n">
+      <c r="L18" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M18" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="N18" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="O18" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу в штатном режиме;</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="P18" s="7" t="inlineStr">
         <is>
           <t>По ГОСТ 10704 п.4: +-0,3 мм, факт 12,42 мм; п.6: +-10%, факт от 1,06 мм до 1,73 мм</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
+      <c r="Q18" s="7" t="n"/>
+    </row>
+    <row r="19" ht="22.95" customHeight="1">
+      <c r="A19" s="3" t="n">
         <v>167</v>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>В00-0000100</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="C19" s="21" t="n"/>
+      <c r="D19" s="22" t="n"/>
+      <c r="E19" s="16" t="inlineStr">
         <is>
           <t>23.06.2026</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000372 от 22.06.2026 8:35:40</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>АСТРЕЯ ООО (ЭДО Такском ЗП согл. от 19.03.2025)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>ПФК(закупка) Элемент закладной ЗФ-30/4/К300-4,5  (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K19" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L19" t="n">
+      <c r="L19" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="M19" t="n">
+      <c r="M19" s="10" t="n">
         <v>1966.05</v>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="N19" s="7" t="inlineStr">
         <is>
           <t>Несоответствие геометрических размеров</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="O19" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="P19" s="7" t="inlineStr">
         <is>
           <t>Деталь №4: Труба 219*8мм, фактически сварена из труб 219*8 и 219*6</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
+      <c r="Q19" s="7" t="n"/>
+    </row>
+    <row r="20" ht="22.95" customHeight="1">
+      <c r="A20" s="3" t="n">
         <v>168</v>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>В00-0000101</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="C20" s="21" t="n"/>
+      <c r="D20" s="22" t="n"/>
+      <c r="E20" s="16" t="inlineStr">
         <is>
           <t>23.06.2026</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000375 от 23.06.2026 8:35:44</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H20" s="7" t="inlineStr">
         <is>
           <t>АСТРЕЯ ООО (ЭДО Такском ЗП согл. от 19.03.2025)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>ПФК(закупка) Элемент закладной ЗФ-30/4/К300-4,5  (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K20" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L20" t="n">
+      <c r="L20" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M20" s="9" t="n">
         <v>218.45</v>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="N20" s="7" t="inlineStr">
         <is>
           <t>Несоответствие геометрических размеров</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="O20" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P20" s="7" t="inlineStr">
         <is>
           <t>Деталь №4: Труба 219*8мм, фактически сварена из труб 219*8 и 219*6</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
+      <c r="Q20" s="7" t="n"/>
+    </row>
+    <row r="21" ht="22.95" customHeight="1">
+      <c r="A21" s="3" t="n">
         <v>169</v>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>В00-0000103</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="C21" s="21" t="n"/>
+      <c r="D21" s="22" t="n"/>
+      <c r="E21" s="16" t="inlineStr">
         <is>
           <t>26.06.2026</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000389 от 26.06.2026 9:24:35</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>ПСК-АРКУС ООО(ЭДО Такском ЗП согл. от 15.06.2026)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Стойка перильного ограждения С2 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K21" s="7" t="inlineStr">
         <is>
           <t>1.01.03 Металлоконструкции для продажи</t>
         </is>
       </c>
-      <c r="L21" t="n">
+      <c r="L21" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M21" s="9" t="n">
         <v>193.23</v>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="N21" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="O21" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="P21" s="7" t="inlineStr">
         <is>
           <t>Брызги металла, плохое повторное возобновление дуги, не заваренный кратер, пора</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
+      <c r="Q21" s="7" t="n"/>
+    </row>
+    <row r="22" ht="22.95" customHeight="1">
+      <c r="A22" s="3" t="n">
         <v>170</v>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>В00-0000103</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="C22" s="21" t="n"/>
+      <c r="D22" s="22" t="n"/>
+      <c r="E22" s="16" t="inlineStr">
         <is>
           <t>26.06.2026</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000389 от 26.06.2026 9:24:35</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22" s="7" t="inlineStr">
         <is>
           <t>ПСК-АРКУС ООО(ЭДО Такском ЗП согл. от 15.06.2026)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I22" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Стойка перильного ограждения С2.1 (пром.) (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K22" s="7" t="inlineStr">
         <is>
           <t>1.01.03 Металлоконструкции для продажи</t>
         </is>
       </c>
-      <c r="L22" t="n">
+      <c r="L22" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M22" s="9" t="n">
         <v>46.05</v>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="N22" s="7" t="inlineStr">
         <is>
           <t>Плохое повторное возбуждение дуги</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="O22" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="P22" s="7" t="inlineStr">
         <is>
           <t>Плохое повторное возбуждение дуги</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
+      <c r="Q22" s="7" t="n"/>
+    </row>
+    <row r="23" ht="22.95" customHeight="1">
+      <c r="A23" s="3" t="n">
         <v>171</v>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>В00-0000103</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="C23" s="21" t="n"/>
+      <c r="D23" s="22" t="n"/>
+      <c r="E23" s="16" t="inlineStr">
         <is>
           <t>26.06.2026</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000389 от 26.06.2026 9:24:35</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H23" s="7" t="inlineStr">
         <is>
           <t>ПСК-АРКУС ООО(ЭДО Такском ЗП согл. от 15.06.2026)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I23" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Стойка перильного ограждения С2.1 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="K23" s="7" t="inlineStr">
         <is>
           <t>1.01.03 Металлоконструкции для продажи</t>
         </is>
       </c>
-      <c r="L23" t="n">
+      <c r="L23" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M23" s="8" t="n">
         <v>404.1</v>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="N23" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="O23" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="P23" s="7" t="inlineStr">
         <is>
           <t>Брызги металла, плохое повторное возобновление дуги, пора, натек. Не выполнено требование КД "заварить".</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
+      <c r="Q23" s="7" t="n"/>
+    </row>
+    <row r="24" ht="22.95" customHeight="1">
+      <c r="A24" s="3" t="n">
         <v>172</v>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
         <is>
           <t>В00-0000103</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="C24" s="21" t="n"/>
+      <c r="D24" s="22" t="n"/>
+      <c r="E24" s="16" t="inlineStr">
         <is>
           <t>26.06.2026</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000389 от 26.06.2026 9:24:35</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H24" s="7" t="inlineStr">
         <is>
           <t>ПСК-АРКУС ООО(ЭДО Такском ЗП согл. от 15.06.2026)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I24" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J24" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Стойка перильного ограждения С3.1 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K24" s="7" t="inlineStr">
         <is>
           <t>1.01.03 Металлоконструкции для продажи</t>
         </is>
       </c>
-      <c r="L24" t="n">
+      <c r="L24" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M24" s="9" t="n">
         <v>39.49</v>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="N24" s="7" t="inlineStr">
         <is>
           <t>Брызги металла</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="O24" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="P24" s="7" t="inlineStr">
         <is>
           <t>Брызги металла</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
+      <c r="Q24" s="7" t="n"/>
+    </row>
+    <row r="25" ht="22.95" customHeight="1">
+      <c r="A25" s="3" t="n">
         <v>173</v>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="16" t="inlineStr">
         <is>
           <t>В00-0000104</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="C25" s="21" t="n"/>
+      <c r="D25" s="22" t="n"/>
+      <c r="E25" s="16" t="inlineStr">
         <is>
           <t>26.06.2026</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000394 от 26.06.2026 16:45:41</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H25" s="7" t="inlineStr">
         <is>
           <t>ПСК-АРКУС ООО(ЭДО Такском ЗП согл. от 15.06.2026)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I25" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J25" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Стойка перильного ограждения С1 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K25" s="7" t="inlineStr">
         <is>
           <t>1.01.03 Металлоконструкции для продажи</t>
         </is>
       </c>
-      <c r="L25" t="n">
+      <c r="L25" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M25" s="9" t="n">
         <v>66.70999999999999</v>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="N25" s="7" t="inlineStr">
         <is>
           <t>Единичные поры</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="O25" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="P25" s="7" t="inlineStr">
         <is>
           <t>Единичная пора</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
+      <c r="Q25" s="7" t="n"/>
+    </row>
+    <row r="26" ht="22.95" customHeight="1">
+      <c r="A26" s="3" t="n">
         <v>174</v>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="16" t="inlineStr">
         <is>
           <t>В00-0000104</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="C26" s="21" t="n"/>
+      <c r="D26" s="22" t="n"/>
+      <c r="E26" s="16" t="inlineStr">
         <is>
           <t>26.06.2026</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000394 от 26.06.2026 16:45:41</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H26" s="7" t="inlineStr">
         <is>
           <t>ПСК-АРКУС ООО(ЭДО Такском ЗП согл. от 15.06.2026)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I26" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J26" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Стойка перильного ограждения С1.1 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K26" s="7" t="inlineStr">
         <is>
           <t>1.01.03 Металлоконструкции для продажи</t>
         </is>
       </c>
-      <c r="L26" t="n">
+      <c r="L26" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M26" s="8" t="n">
         <v>94.40000000000001</v>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="N26" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="O26" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="P26" s="7" t="inlineStr">
         <is>
           <t>Брызги металла, пора, незаваренный кратер</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
+      <c r="Q26" s="7" t="n"/>
+    </row>
+    <row r="27" ht="22.95" customHeight="1">
+      <c r="A27" s="3" t="n">
         <v>175</v>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>В00-0000104</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="C27" s="21" t="n"/>
+      <c r="D27" s="22" t="n"/>
+      <c r="E27" s="16" t="inlineStr">
         <is>
           <t>26.06.2026</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000394 от 26.06.2026 16:45:41</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H27" s="7" t="inlineStr">
         <is>
           <t>ПСК-АРКУС ООО(ЭДО Такском ЗП согл. от 15.06.2026)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I27" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J27" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Стойка перильного ограждения С3 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K27" s="7" t="inlineStr">
         <is>
           <t>1.01.03 Металлоконструкции для продажи</t>
         </is>
       </c>
-      <c r="L27" t="n">
+      <c r="L27" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M27" t="n">
+      <c r="M27" s="3" t="n">
         <v>59</v>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="N27" s="7" t="inlineStr">
         <is>
           <t>Натек</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="O27" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="P27" s="7" t="inlineStr">
         <is>
           <t>Натек металла</t>
         </is>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
+      <c r="Q27" s="7" t="n"/>
+    </row>
+    <row r="28" ht="22.95" customHeight="1">
+      <c r="A28" s="3" t="n">
         <v>176</v>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="16" t="inlineStr">
         <is>
           <t>В00-0000105</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="C28" s="21" t="n"/>
+      <c r="D28" s="22" t="n"/>
+      <c r="E28" s="16" t="inlineStr">
         <is>
           <t>30.06.2026</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="19" t="inlineStr">
         <is>
           <t>Приобретение товаров и услуг 0000-002805 от 24.06.2026 23:59:59</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" s="20" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H28" s="7" t="inlineStr">
         <is>
           <t>ТД ЭЛЕКТРОТЕХМОНТАЖ АО (ЭТМ)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>Основной склад</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J28" s="7" t="inlineStr">
         <is>
           <t>_уу_Шкаф распределительный ЩВ1 + 3 КЗНС МФГ25-М(500)-IV-3-цл (23М)</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K28" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L28" t="n">
+      <c r="L28" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="M28" s="13" t="n"/>
+      <c r="N28" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="O28" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Взять в работу в штатном режиме;</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="P28" s="7" t="inlineStr">
         <is>
           <t>Акт во вложении.</t>
         </is>
       </c>
+      <c r="Q28" s="7" t="n"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <autoFilter ref="A1:Q28">
+    <filterColumn colId="1" hiddenButton="0" showButton="0"/>
+    <filterColumn colId="2" hiddenButton="0" showButton="0"/>
+  </autoFilter>
+  <mergeCells count="28">
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.3937007874015748" bottom="0.3937007874015748" header="0" footer="0"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" pageOrder="overThenDown"/>
 </worksheet>
 </file>